--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121679047</v>
+        <v>121681249</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628215</v>
+        <v>628068</v>
       </c>
       <c r="R2" t="n">
-        <v>6896820</v>
+        <v>6896792</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ett flertal gamla blomstänglar och bladrosetter under snön. Svårt att räkna pga snöläget.</t>
+          <t>Tall med många ringhack, svårt att bedöma ålder.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121678694</v>
+        <v>121679047</v>
       </c>
       <c r="B3" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +809,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628250</v>
+        <v>628215</v>
       </c>
       <c r="R3" t="n">
-        <v>6896791</v>
+        <v>6896820</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,6 +883,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett flertal gamla blomstänglar och bladrosetter under snön. Svårt att räkna pga snöläget.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121679301</v>
+        <v>121678694</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +926,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628148</v>
+        <v>628250</v>
       </c>
       <c r="R4" t="n">
-        <v>6896847</v>
+        <v>6896791</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121681249</v>
+        <v>121679301</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,43 +1038,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628068</v>
+        <v>628148</v>
       </c>
       <c r="R5" t="n">
-        <v>6896792</v>
+        <v>6896847</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tall med många ringhack, svårt att bedöma ålder.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681249</v>
+        <v>121679301</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628068</v>
+        <v>628148</v>
       </c>
       <c r="R2" t="n">
-        <v>6896792</v>
+        <v>6896847</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tall med många ringhack, svårt att bedöma ålder.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121679047</v>
+        <v>121678694</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>90693</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628215</v>
+        <v>628250</v>
       </c>
       <c r="R3" t="n">
-        <v>6896820</v>
+        <v>6896791</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,11 +873,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett flertal gamla blomstänglar och bladrosetter under snön. Svårt att räkna pga snöläget.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121678694</v>
+        <v>121679047</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628250</v>
+        <v>628215</v>
       </c>
       <c r="R4" t="n">
-        <v>6896791</v>
+        <v>6896820</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,6 +985,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett flertal gamla blomstänglar och bladrosetter under snön. Svårt att räkna pga snöläget.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121679301</v>
+        <v>121681249</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1028,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628148</v>
+        <v>628068</v>
       </c>
       <c r="R5" t="n">
-        <v>6896847</v>
+        <v>6896792</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tall med många ringhack, svårt att bedöma ålder.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121681249</v>
       </c>
       <c r="B2" t="n">
-        <v>57369</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121681249</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121681249</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121681249</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,6 +1136,113 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133654704</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>628100</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6896829</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>133654704</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -1141,7 +1141,7 @@
         <v>133654704</v>
       </c>
       <c r="B6" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681249</v>
+        <v>121678694</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628068</v>
+        <v>628250</v>
       </c>
       <c r="R2" t="n">
-        <v>6896792</v>
+        <v>6896791</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tall med många ringhack, svårt att bedöma ålder.</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,50 +782,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121679301</v>
+        <v>121681249</v>
       </c>
       <c r="B3" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628148</v>
+        <v>628068</v>
       </c>
       <c r="R3" t="n">
-        <v>6896847</v>
+        <v>6896792</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tall med många ringhack, svårt att bedöma ålder.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,53 +899,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121678694</v>
+        <v>133654704</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628250</v>
+        <v>628100</v>
       </c>
       <c r="R4" t="n">
-        <v>6896791</v>
+        <v>6896829</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,12 +994,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1024,12 +1009,7 @@
         <v>121679047</v>
       </c>
       <c r="B5" t="n">
-        <v>98149</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,58 +1118,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133654704</v>
+        <v>121679301</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hinrik-Hansbäcken, Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628100</v>
+        <v>628148</v>
       </c>
       <c r="R6" t="n">
-        <v>6896829</v>
+        <v>6896847</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,12 +1183,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,12 +1213,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 55550-2024 artfynd.xlsx
+++ b/artfynd/A 55550-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121678694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121681249</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133654704</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121679047</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,8 +1247,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121679301</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>